--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.36359384122778</v>
+        <v>10.29658399919951</v>
       </c>
       <c r="D2" t="n">
-        <v>63.41553111072415</v>
+        <v>10.30502380549268</v>
       </c>
       <c r="E2" t="n">
-        <v>10.64671826389484</v>
+        <v>1.730091717882912</v>
       </c>
       <c r="F2" t="n">
-        <v>10.59125029254331</v>
+        <v>1.721078172538288</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.90175333103279</v>
+        <v>8.921534916292828</v>
       </c>
       <c r="D3" t="n">
-        <v>54.99984765825185</v>
+        <v>8.937475244465926</v>
       </c>
       <c r="E3" t="n">
-        <v>10.64671826389484</v>
+        <v>1.730091717882912</v>
       </c>
       <c r="F3" t="n">
-        <v>10.59125029254331</v>
+        <v>1.721078172538288</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.00902159124062</v>
+        <v>7.313966008576601</v>
       </c>
       <c r="D4" t="n">
-        <v>45.03699707046655</v>
+        <v>7.318512023950814</v>
       </c>
       <c r="E4" t="n">
-        <v>10.64671826389484</v>
+        <v>1.730091717882912</v>
       </c>
       <c r="F4" t="n">
-        <v>10.59125029254331</v>
+        <v>1.721078172538288</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.84119229560326</v>
+        <v>9.72419374803553</v>
       </c>
       <c r="D5" t="n">
-        <v>59.7777634006198</v>
+        <v>9.713886552600718</v>
       </c>
       <c r="E5" t="n">
-        <v>10.64671826389484</v>
+        <v>1.730091717882912</v>
       </c>
       <c r="F5" t="n">
-        <v>10.59125029254331</v>
+        <v>1.721078172538288</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.01617741199889</v>
+        <v>5.52762882944982</v>
       </c>
       <c r="D6" t="n">
-        <v>33.92749047462306</v>
+        <v>5.513217202126246</v>
       </c>
       <c r="E6" t="n">
-        <v>10.64671826389484</v>
+        <v>1.730091717882912</v>
       </c>
       <c r="F6" t="n">
-        <v>10.59125029254331</v>
+        <v>1.721078172538288</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.36402215284814</v>
+        <v>8.671653599837823</v>
       </c>
       <c r="D7" t="n">
-        <v>52.92457061315337</v>
+        <v>8.600242724637424</v>
       </c>
       <c r="E7" t="n">
-        <v>10.64671826389484</v>
+        <v>1.730091717882912</v>
       </c>
       <c r="F7" t="n">
-        <v>10.59125029254331</v>
+        <v>1.721078172538288</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.75058244600535</v>
+        <v>7.434469647475869</v>
       </c>
       <c r="D8" t="n">
-        <v>45.48262060102952</v>
+        <v>7.390925847667297</v>
       </c>
       <c r="E8" t="n">
-        <v>10.64671826389484</v>
+        <v>1.730091717882912</v>
       </c>
       <c r="F8" t="n">
-        <v>10.59125029254331</v>
+        <v>1.721078172538288</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.71676031135733</v>
+        <v>5.966473550595566</v>
       </c>
       <c r="D9" t="n">
-        <v>36.32405498624264</v>
+        <v>5.90265893526443</v>
       </c>
       <c r="E9" t="n">
-        <v>10.64671826389484</v>
+        <v>1.730091717882912</v>
       </c>
       <c r="F9" t="n">
-        <v>10.59125029254331</v>
+        <v>1.721078172538288</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.66509960664474</v>
+        <v>5.30807868607977</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31605648700758</v>
+        <v>5.413859179138732</v>
       </c>
       <c r="E10" t="n">
-        <v>10.64671826389484</v>
+        <v>1.730091717882912</v>
       </c>
       <c r="F10" t="n">
-        <v>10.59125029254331</v>
+        <v>1.721078172538288</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
